--- a/docs/業務詳細.xlsx
+++ b/docs/業務詳細.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugur\Deploy\相続プラットフォーム\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9B35C39E-2CCB-4909-B6C2-3D8090AB45F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE00B1-DD80-4FAF-80B7-033C9FC10425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{53D2D5B1-C6AD-489D-929F-7FB5AB038F7C}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53D2D5B1-C6AD-489D-929F-7FB5AB038F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="116">
   <si>
     <t>登記</t>
   </si>
@@ -71,9 +72,6 @@
   </si>
   <si>
     <t>執行</t>
-  </si>
-  <si>
-    <t>コンサル</t>
   </si>
   <si>
     <t>手続き一式</t>
@@ -194,38 +192,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>まずない
-五十嵐登記T</t>
-    <rPh sb="5" eb="8">
-      <t>イガラシ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トウキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>書類チェック</t>
-    <rPh sb="0" eb="2">
-      <t>ショルイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>チェック</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>相続登記</t>
-    <rPh sb="0" eb="2">
-      <t>ソウゾク</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>トウキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>オーシャン：依頼者＝6：4、7：3</t>
     <rPh sb="6" eb="9">
       <t>イライシャ</t>
@@ -241,6 +207,10 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>固定資産評価証明取得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>固定資産評価の確認</t>
     <rPh sb="7" eb="9">
       <t>カクニン</t>
@@ -267,19 +237,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>このときだけオーダーシートの遺言セクション、タブの遺言タブを作成</t>
-    <rPh sb="14" eb="16">
-      <t>ユイゴン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ユイゴン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>遺言作成(自筆）</t>
     <rPh sb="0" eb="2">
       <t>ユイゴン</t>
@@ -293,19 +250,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>遺言文案作成</t>
-    <rPh sb="0" eb="2">
-      <t>ユイゴン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ブンアン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>遺言作成(公正証書）</t>
     <rPh sb="0" eb="2">
       <t>ユイゴン</t>
@@ -315,41 +259,6 @@
     </rPh>
     <rPh sb="5" eb="9">
       <t>コウセイショウショ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>文案確認・公証役場に事前チェック・日程調整</t>
-    <rPh sb="0" eb="2">
-      <t>ブンアン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>カクニン</t>
-    </rPh>
-    <rPh sb="5" eb="9">
-      <t>コウショウヤクバ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ジゼン</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ニッテイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>お客さんに日程伝える</t>
-    <rPh sb="1" eb="2">
-      <t>キャク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニッテイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ツタ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -454,31 +363,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>いきなり放棄受注ケースもあるけど、手続き一式で財産調査した結果放棄になる。</t>
-    <rPh sb="4" eb="6">
-      <t>ホウキ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジュチュウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>テツヅ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>イッシキ</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>ザイサンチョウサ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ケッカ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>ホウキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>放棄の申述書類作成</t>
     <rPh sb="0" eb="2">
       <t>ホウキ</t>
@@ -652,41 +536,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>自筆証書遺言があったときに、家庭裁判所に遺言書あるよお墨付きある</t>
-    <rPh sb="0" eb="2">
-      <t>ジヒツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ショウショ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ユイゴン</t>
-    </rPh>
-    <rPh sb="14" eb="19">
-      <t>カテイサイバンショ</t>
-    </rPh>
-    <rPh sb="20" eb="23">
-      <t>イゴンショ</t>
-    </rPh>
-    <rPh sb="27" eb="29">
-      <t>スミツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>検認したあとに手続き一式につながる。</t>
-    <rPh sb="0" eb="2">
-      <t>ケンニン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>テツヅ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>イッシキ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>検認手続き</t>
     <rPh sb="2" eb="4">
       <t>テツヅ</t>
@@ -989,12 +838,322 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>全部空にします。</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンブ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>カラ</t>
+    <t>戸籍収集（請求・取得）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戸籍チェック</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相関図作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>法定相続情報一覧図の申出・取得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>残高証明取得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>取引履歴取得</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>保険照会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全店調査</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>証券保管振替機構照会</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>財産目録の作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>備考</t>
+    <rPh sb="0" eb="2">
+      <t>ビコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2/3はお客さんが広域交付制度で取得</t>
+    <rPh sb="5" eb="6">
+      <t>キャク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウイキ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>コウフ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>セイド</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>シュトク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>10割オーシャン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9割オーシャン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9割以上オーシャンさん。不動産はまとめて依頼が多い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遺産分割協議書の作成</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>相続登記の申請</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>預貯金の解約</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>証券の移管・売却</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>投資信託の解約</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>半々くらい依頼者がやる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>各相続人への通知・案内文の送付</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>査定の依頼</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>協議書のチェック</t>
+    <rPh sb="0" eb="3">
+      <t>キョウギショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不動産関連書類チェック</t>
+    <rPh sb="0" eb="3">
+      <t>フドウサン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カンレン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ショルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>公証役場訪問日程の共有</t>
+    <rPh sb="0" eb="4">
+      <t>コウショウヤクバ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ホウモン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニッテイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キョウユウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>文案確認・公証役場訪問の日程調整</t>
+    <rPh sb="0" eb="2">
+      <t>ブンアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウショウヤクバ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウモン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニッテイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>チョウセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遺言文案(自筆)作成</t>
+    <rPh sb="0" eb="2">
+      <t>ユイゴン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンアン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジヒツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>遺言文案(公正証書)作成</t>
+    <rPh sb="0" eb="2">
+      <t>ユイゴン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブンアン</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>コウセイショウショ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金融資産が記載されている資料の確認</t>
+    <rPh sb="0" eb="2">
+      <t>キンユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シサン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>信託契約書作成</t>
+    <rPh sb="0" eb="2">
+      <t>シンタク</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>ケイヤクショ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>自筆証書遺言があったときに、家庭裁判所に遺言書あるよお墨付きある。検認したあとに手続き一式につながる。</t>
+    <rPh sb="0" eb="2">
+      <t>ジヒツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ショウショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ユイゴン</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>カテイサイバンショ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>イゴンショ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>スミツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>執行人通知</t>
+    <rPh sb="0" eb="3">
+      <t>シッコウニン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>実施者割合</t>
+    <rPh sb="0" eb="3">
+      <t>ジッシシャ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ワリアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発生することはあまりない</t>
+    <rPh sb="0" eb="2">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9割以上オーシャンさん。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>不動産はまとめて依頼が多い</t>
+  </si>
+  <si>
+    <t>いきなり放棄受注ケースもあるけど、手続き一式で財産調査した結果放棄になるケースが多い。</t>
+    <rPh sb="4" eb="6">
+      <t>ホウキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ジュチュウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>テツヅ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>イッシキ</t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t>ザイサンチョウサ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ホウキ</t>
+    </rPh>
+    <rPh sb="40" eb="41">
+      <t>オオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1003,7 +1162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1028,21 +1187,50 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1051,21 +1239,33 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,868 +1601,2078 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6CE2767-BCA1-4387-A334-79213DB423AA}">
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="17.58203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.25" style="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="24.6640625" customWidth="1"/>
     <col min="4" max="4" width="41.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30.4140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="74.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3">
+        <f>ROW()-1</f>
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3">
+        <f t="shared" ref="A3:A66" si="0">ROW()-1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="3">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="3">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="3">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="3">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="3">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F15" s="4"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="3">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="3">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="3">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="3">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="3">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="3">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="3">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="2" t="s">
+      <c r="D22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="3">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="4"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="3">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="4"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="3">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25" s="4"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="3">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="3">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="3">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="4"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="3">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="3">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F30" s="4"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="3">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F31" s="4"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="3">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F32" s="4"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="4"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="3">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="4"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="3">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="4"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="3">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="4"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="3">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="3">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="4"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="3">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" s="4"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="3">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="4"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="4"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="3">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="4"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="3">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="4"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="3">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="4"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="3">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="4"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="3">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="4"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="3">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="4"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="3">
+        <f t="shared" si="0"/>
+        <v>47</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="4"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="3">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="4"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="3">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="4"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="3">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" s="3">
+        <f t="shared" si="0"/>
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="4"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" s="3">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="4"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="3">
+        <f t="shared" si="0"/>
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="4"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="3">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="4"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="3">
+        <f t="shared" si="0"/>
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="4"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="3">
+        <f t="shared" si="0"/>
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="3">
+        <f t="shared" si="0"/>
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="4"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="3">
+        <f t="shared" si="0"/>
+        <v>58</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="3">
+        <f t="shared" si="0"/>
+        <v>59</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="4"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="3">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F61" s="4"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" s="3">
+        <f t="shared" si="0"/>
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" s="3">
+        <f t="shared" si="0"/>
+        <v>62</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="4"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" s="3">
+        <f t="shared" si="0"/>
+        <v>63</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" s="3">
+        <f t="shared" si="0"/>
+        <v>64</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="4"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" s="3">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F66" s="4"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" s="3">
+        <f t="shared" ref="A67:A109" si="1">ROW()-1</f>
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F67" s="4"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" s="3">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F68" s="4"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" s="3">
+        <f t="shared" si="1"/>
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F69" s="4"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" s="3">
+        <f t="shared" si="1"/>
+        <v>69</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" s="3">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" s="3">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F72" s="4"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" s="3">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" s="3">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="4"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" s="3">
+        <f t="shared" si="1"/>
+        <v>74</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" s="3">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F76" s="4"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" s="3">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F77" s="4"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" s="3">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" s="3">
+        <f t="shared" si="1"/>
+        <v>78</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79" s="4"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" s="3">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="4"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" s="3">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F81" s="4"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" s="3">
+        <f t="shared" si="1"/>
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F82" s="4"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" s="3">
+        <f>ROW()-1</f>
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F83" s="4"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" s="3">
+        <f t="shared" si="1"/>
+        <v>83</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" s="3">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F85" s="4"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" s="3">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F86" s="4"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" s="3">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" s="3">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" s="3">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D89" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" s="4"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" s="3">
+        <f t="shared" si="1"/>
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" s="3">
+        <f t="shared" si="1"/>
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" s="3">
+        <f t="shared" si="1"/>
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C3" t="s">
+      <c r="D92" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F92" s="4"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" s="3">
+        <f t="shared" si="1"/>
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C4" t="s">
+      <c r="D93" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F93" s="4"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" s="3">
+        <f t="shared" si="1"/>
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C5" t="s">
+      <c r="D94" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" s="4"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" s="3">
+        <f t="shared" si="1"/>
+        <v>94</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F95" s="4"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" s="3">
+        <f t="shared" si="1"/>
+        <v>95</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="4"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" s="3">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C7" t="s">
+      <c r="D97" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E97" s="4"/>
+      <c r="F97" s="4"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" s="3">
+        <f t="shared" si="1"/>
+        <v>97</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" s="3">
+        <f t="shared" si="1"/>
+        <v>98</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" s="3">
+        <f t="shared" si="1"/>
+        <v>99</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" s="3">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" s="3">
+        <f t="shared" si="1"/>
+        <v>101</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" s="3">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C8" t="s">
+      <c r="D103" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F103" s="4"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" s="3">
+        <f t="shared" si="1"/>
+        <v>103</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F104" s="4"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" s="3">
+        <f t="shared" si="1"/>
+        <v>104</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="4" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C9" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C10" t="s">
+      <c r="D105" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F105" s="4"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" s="3">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F106" s="4"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" s="3">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E107" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F107" s="4"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" s="3">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" s="3">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="36" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B14" s="2"/>
-      <c r="D14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B15" s="2"/>
-      <c r="C15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="B16" s="2"/>
-      <c r="C16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" t="s">
-        <v>33</v>
-      </c>
-      <c r="E16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B17" s="2"/>
-      <c r="C17" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B18" s="2"/>
-      <c r="C18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B20" s="2"/>
-      <c r="D20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B21" s="2"/>
-      <c r="C21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="2"/>
-      <c r="D22" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B23" s="2"/>
-      <c r="D23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B24" s="2"/>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s">
-        <v>40</v>
-      </c>
-      <c r="E24" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B25" s="2"/>
-      <c r="C25" t="s">
-        <v>42</v>
-      </c>
-      <c r="D25" t="s">
-        <v>43</v>
-      </c>
-      <c r="E25" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B26" s="2"/>
-      <c r="C26" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B27" s="2"/>
-      <c r="D27" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B28" s="2"/>
-      <c r="D28" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D29" t="s">
-        <v>47</v>
-      </c>
-      <c r="E29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" t="s">
-        <v>25</v>
-      </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D31" t="s">
-        <v>26</v>
-      </c>
-      <c r="E31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D34" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C35" t="s">
-        <v>16</v>
-      </c>
-      <c r="D35" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C37" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D38" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C41" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E42" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D43" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" t="s">
-        <v>37</v>
-      </c>
-      <c r="E44" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D45" t="s">
-        <v>38</v>
-      </c>
-      <c r="E45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D46" t="s">
-        <v>39</v>
-      </c>
-      <c r="E46" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C47" t="s">
-        <v>16</v>
-      </c>
-      <c r="D47" t="s">
-        <v>40</v>
-      </c>
-      <c r="E47" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C48" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D49" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D50" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D51" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D52" t="s">
-        <v>62</v>
-      </c>
-      <c r="E52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D53" t="s">
-        <v>63</v>
-      </c>
-      <c r="F53" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D54" t="s">
-        <v>64</v>
-      </c>
-      <c r="E54" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" t="s">
-        <v>68</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C55" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="2"/>
-      <c r="D56" t="s">
-        <v>26</v>
-      </c>
-      <c r="E56" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="2"/>
-      <c r="C57" t="s">
-        <v>15</v>
-      </c>
-      <c r="D57" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="2"/>
-      <c r="D58" t="s">
-        <v>38</v>
-      </c>
-      <c r="E58" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="2"/>
-      <c r="D59" t="s">
-        <v>39</v>
-      </c>
-      <c r="E59" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="2"/>
-      <c r="C60" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" t="s">
-        <v>40</v>
-      </c>
-      <c r="E60" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="2"/>
-      <c r="C61" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A62" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" t="s">
-        <v>24</v>
-      </c>
-      <c r="D62" t="s">
-        <v>25</v>
-      </c>
-      <c r="E62" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A63" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="2"/>
-      <c r="D63" t="s">
-        <v>26</v>
-      </c>
-      <c r="E63" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="2"/>
-      <c r="C64" t="s">
-        <v>71</v>
-      </c>
-      <c r="D64" t="s">
-        <v>72</v>
-      </c>
-      <c r="E64" t="s">
-        <v>28</v>
-      </c>
-      <c r="F64" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="2"/>
-      <c r="D65" t="s">
-        <v>73</v>
-      </c>
-      <c r="E65" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="2"/>
-      <c r="D66" t="s">
-        <v>74</v>
-      </c>
-      <c r="E66" t="s">
-        <v>28</v>
-      </c>
-      <c r="F66" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="2"/>
-      <c r="D67" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="2"/>
-      <c r="D68" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A69" t="s">
-        <v>78</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" t="s">
-        <v>25</v>
-      </c>
-      <c r="E69" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="2"/>
-      <c r="D70" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="2"/>
-      <c r="C71" t="s">
-        <v>15</v>
-      </c>
-      <c r="D71" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="2"/>
-      <c r="D72" t="s">
-        <v>38</v>
-      </c>
-      <c r="E72" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="2"/>
-      <c r="D73" t="s">
-        <v>39</v>
-      </c>
-      <c r="E73" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="2"/>
-      <c r="C74" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74" t="s">
-        <v>40</v>
-      </c>
-      <c r="E74" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="C75" t="s">
-        <v>79</v>
-      </c>
-      <c r="D75" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D76" t="s">
-        <v>80</v>
-      </c>
-      <c r="E76" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="D77" t="s">
-        <v>82</v>
-      </c>
-      <c r="E77" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C78" t="s">
-        <v>87</v>
-      </c>
-      <c r="D78" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="2"/>
-      <c r="D79" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C81" t="s">
-        <v>83</v>
-      </c>
-      <c r="D81" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C82" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C83" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C84" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C85" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C86" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C87" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C88" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C89" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C90" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="C91" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.55000000000000004">
-      <c r="B92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" t="s">
-        <v>88</v>
-      </c>
+      <c r="D109" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE42F0A-A37F-4DA4-B274-046934718FC5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/業務詳細.xlsx
+++ b/docs/業務詳細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sugur\Deploy\相続プラットフォーム\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE00B1-DD80-4FAF-80B7-033C9FC10425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6658C5A-A5AB-4732-91D1-2C9E33ED9978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{53D2D5B1-C6AD-489D-929F-7FB5AB038F7C}"/>
+    <workbookView xWindow="38235" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{53D2D5B1-C6AD-489D-929F-7FB5AB038F7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="122">
   <si>
     <t>登記</t>
   </si>
@@ -1154,6 +1154,69 @@
     </rPh>
     <rPh sb="40" eb="41">
       <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>契約書</t>
+    <rPh sb="0" eb="3">
+      <t>ケイヤクショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>委任状</t>
+    <rPh sb="0" eb="3">
+      <t>イニンジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>本人確認書類</t>
+    <rPh sb="0" eb="2">
+      <t>ホンニン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ショルイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>印鑑証明書</t>
+    <rPh sb="0" eb="4">
+      <t>インカンショウメイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ショ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>戸籍</t>
+    <rPh sb="0" eb="2">
+      <t>コセキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初にもらった分の戸籍を見て、どこまでの戸籍</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コセキ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>コセキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -3669,9 +3732,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE42F0A-A37F-4DA4-B274-046934718FC5}">
-  <dimension ref="A1"/>
+  <dimension ref="B2:C6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="B6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
